--- a/tools/pet-grooming-receipt-form/儲值客戶服務簽收單.xlsx
+++ b/tools/pet-grooming-receipt-form/儲值客戶服務簽收單.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>客戶姓名</t>
+          <t>寵物名</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
